--- a/docs/ACOLHE_municipios.xlsx
+++ b/docs/ACOLHE_municipios.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -639,12 +639,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Coronel Xavier Chaves / MG</t>
+          <t>Maracás / BA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>É o contato mais completo que existe na pasta: e-mail, telefone COM RAMAL e WhatsApp, todos impressos no próprio edital. Município pequeno, o programa é do CRAS, e o edital é recente e bem escrito. Maior chance de alguém atender e conversar.</t>
+          <t>O objeto publicado é o mais completo de todos: diz o público (gestantes em vulnerabilidade, sede E zona rural), o canal (CRAS), a secretaria (Desenvolvimento Social) e o amparo legal (Benefício Eventual–Natalidade). Setor de licitações verificado em edital no domínio do município, com telefone da Equipe de Pregão. Foi uma DISPENSA de R$60.910 — o tipo de compra que você pode disputar primeiro.</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>São Pedro do Iguaçu / PR</t>
+          <t>Coronel Xavier Chaves / MG</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>O único edital que publica o e-mail do DEPARTAMENTO DE ASSISTÊNCIA SOCIAL direto, não o da licitação. É a conversa A sem intermediário.</t>
+          <t>O contato mais completo da pasta: e-mail, telefone COM RAMAL e WhatsApp, impressos no próprio edital, com o horário de expediente do setor ao lado. Município pequeno, programa do CRAS. Maior chance de alguém simplesmente atender.</t>
         </is>
       </c>
     </row>
@@ -673,12 +673,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Belterra / PA</t>
+          <t>São Pedro do Iguaçu / PR</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>O termo de referência inteiro é da SEMTDES e traz o e-mail dela em cada página. Município do Pará, kit entregue via CRAS — perfil exato do seu cliente-alvo, e longe de São Paulo.</t>
+          <t>O único edital que publica o e-mail do DEPARTAMENTO DE ASSISTÊNCIA SOCIAL direto, não o da licitação. É a conversa A sem intermediário.</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Bocaiúva do Sul / PR</t>
+          <t>Belterra / PA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Setor de compras com telefone direto. Bom para a conversa B.</t>
+          <t>O termo de referência inteiro é da SEMTDES e traz o e-mail dela em cada página. Município do Pará, kit entregue via CRAS — perfil exato do seu cliente-alvo, e longe de São Paulo.</t>
         </is>
       </c>
     </row>
@@ -707,53 +707,71 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>Bocaiúva do Sul / PR</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Setor de compras com telefone direto. Bom para a conversa B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>6º</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
           <t>Irecê / BA</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Pregão de até 400 kits, agente de contratação nomeado no edital. Maior volume da pasta — bom para entender um comprador maior.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TRÊS REGRAS</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Não ofereça nada, não mande catálogo, não peça para ser cadastrada como fornecedora. No momento em que virar venda, a conversa acaba e a porta fecha.</t>
-        </is>
-      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Ligue em horário de expediente do interior: 8h–11h ou 13h–16h. Muita prefeitura pequena fecha ao meio-dia.</t>
+          <t>Não ofereça nada, não mande catálogo, não peça para ser cadastrada como fornecedora. No momento em que virar venda, a conversa acaba e a porta fecha.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>Ligue em horário de expediente do interior: 8h–11h ou 13h–16h. Muita prefeitura pequena fecha ao meio-dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Se pedirem para você formalizar por e-mail, formalize — e guarde a resposta. Um servidor explicando o programa por escrito vale mais que dez editais.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="A4:F4"/>
@@ -772,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1176,53 +1194,253 @@
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Itaquaquecetuba</t>
+          <t>Maracás</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Kit maternidade, 17 itens, SRP (PE 90088/2025) — o kit que o BOM inteiro copia</t>
+          <t>DISPENSA — Kit Enxoval de Bebê p/ gestantes em vulnerabilidade, sede e zona rural, via CRAS, no âmbito do Benefício Eventual–Natalidade (R$60.910)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>não publicado no que foi lido</t>
+          <t>Setor de Licitações · Equipe de Pregão</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>licitacoesmaracas@gmail.com · prefeitura@maracas.ba.gov.br</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(73) 3533-2121 · Equipe de Pregão (73) 99823-6264 · WhatsApp (73) 99151-7240</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Registro do PNCP; o edital em PDF não pôde ser baixado (Família B fora do ar)</t>
+          <t>Edital PDF no domínio municipal; Praça Ruy Barbosa 705. Pop. 27.620</t>
         </is>
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Faltam aqui os cinco municípios da varredura de 15/09 — Alvorada de Minas/MG, Maracás/BA, Vitória/ES, Junco do Maranhão/MA e Rio Branco do Sul/PR. Os contatos deles estão sendo levantados e entram nesta aba quando estiverem confirmados na fonte.</t>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>PREGÃO — RP Kit Bebê, R$944.586 (15x o segundo maior). Comprado pela prefeitura, não por fundo</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>SEMAS (Assistência Social) · SEGES/CPL (pregão)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>rspuppim@vitoria.es.gov.br (Equipe de Pregão)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>SEMAS (27) 3382-6172 · Pregão (27) 3382-6074 / 6037 · CPL (27) 3382-6253</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Portal de compras do município e páginas da SEMAS. Pop. 322.869</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Alvorada de Minas</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>PREGÃO — RP «enxovais» para UNIDADES DE SAÚDE e casa de apoio (R$41.665). ⚠ comprado pela Sec. de SAÚDE, não pela Assistência Social</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Divisão de Compras e Licitações · Sec. de Saúde</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>licitacao@alvoradademinas.mg.gov.br · saude@alvoradademinas.mg.gov.br</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>(31) 3520-0000 / 3520-0001 · Assist. Social (31) 3862-1209</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Site municipal, sub-rota /licitacoes/pregao-eletronico. Pop. 4.159</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Junco do Maranhão</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — itens para kits enxoval de recém-nascidos (R$11.621, o menor do dia). Compra pelo FMAS</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Gabinete (único canal encontrado)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>gabinete@juncodomaranhao.ma.gov.br</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>(98) 3271-1017</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Portal da transparência. ⚠ O site institucional publica dados de EXEMPLO (contato@prefeitura.gov.br, (00) 0000-0000) — não use. Pop. 5.146</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Rio Branco do Sul</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA PDE 31 — kit natalidade, entrega parcelada por 12 MESES (R$16.520). A que fechou antes de vermos. Compra pelo FMAS</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Ouvidoria (único canal encontrado)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>ouvidoria@riobrancodosul.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>(41) 98743-2024</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Rodapé do diário oficial. O portal atende.net é só JavaScript: nenhum telefone de licitações ou do CRAS é legível. Pop. 37.558</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Itaquaquecetuba</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Kit maternidade, 17 itens, SRP (PE 90088/2025) — o kit que o BOM inteiro copia</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>não publicado no que foi lido</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Registro do PNCP; o edital em PDF não pôde ser baixado (Família B fora do ar)</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Contatos completos e linha a linha em data/municipios_contatos.csv (60 registros) e data/municipios_contatos.md. Nada aqui foi inventado: cada valor foi lido numa página oficial do município, no diário oficial ou no edital publicado. Onde não deu para ler, está escrito que não deu.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1448,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C12"/>
+  <dimension ref="B1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1554,8 +1772,56 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
+    <row r="11" ht="42" customHeight="1">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>O amparo legal</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Quase nunca é um «programa» com nome. É BENEFÍCIO EVENTUAL do SUAS, criado por RESOLUÇÃO DO CMAS, não por lei municipal. Pergunte «qual resolução do CMAS ampara?» — essa pergunta abre porta; «vocês têm um programa mãe?» não.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Estado x município</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Há programas estaduais por cima: Maranhão Acolhe (lançado dez/2025, kit de 45 ITENS com bolsa personalizada) e Nascer Bem no Paraná. As compras municipais parecem COMPLEMENTAR a entrega estadual, não substituí-la. Em MA, o kit de 45 itens é a referência de conteúdo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Atenção a Vitória</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>O «Benefício por Natalidade» de Vitória é pago EM DINHEIRO, parcela única (Resolução 016/2017 do COMASV). Então o Kit Bebê de R$944k é outro programa, e não foi possível achar o instrumento que o autoriza. É uma ótima pergunta para levar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Atenção a Alvorada de Minas</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Comprada pela Secretaria de SAÚDE, destino «unidades de saúde e casa de apoio». «Enxoval» ali pode ser roupa de cama hospitalar, não enxoval de bebê. É a única das cinco que não passa pela assistência social — confirmar antes de tratar como comparável.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>O que NENHUM edital responde, e por isso vale a ligação: quantos concorrentes aparecem, se já deu deserto, quantos dias o pagamento leva DE VERDADE, se aceitam atestado privado, e o que as mães acham do kit.</t>
         </is>
@@ -1563,7 +1829,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/ACOLHE_municipios.xlsx
+++ b/docs/ACOLHE_municipios.xlsx
@@ -790,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1431,8 +1431,720 @@
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="10" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Maracás</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISPENSA — Contratação de empresa especializada para o fornecimento de Kit Enxoval de Bebê, destinado ao atendimento de gestantes em situação de vulnerabilidade </t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE MARACAS</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>licitacoesmaracas@gmail.com · departamentoadmsocial1@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-15.</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Feira de Santana</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — AQUISIÇÃO DE KITS ENXOVAL PARA BEBÊS OS KITS DEVERÃO ATENDER ÀS NECESSIDADES DO HOSPITAL INÁCIA PINTO DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>FUNDACAO HOSPITALAR DE FEIRA DE SANTANA</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. ATENÇÃO: um telefone foi descartado por ser da plataforma de licitação, não do município. Publicado 2026-08-10.</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Groaíras</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>CE</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — AQUISIÇÃO DE ITENS DIVERSOS DESTINADOS À COMPOSIÇÃO DE KITS NATALIDADE, COM O OBJETIVO DE SUPRIR AS NECESSIDADES DE ENXOVAL BÁSICO PARA RECÉM-NASCIDOS</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE GROAIRAS</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>licitacao@groairas.ce.gov.br</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-07-01.</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Junco do Maranhão</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — Contratação de empresa especializada para Fornecimento de itens para kits enxoval de recém-nascidos, para distribuição às gestantes em situação de vul</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE JUNCO DO MARANHAO</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>prefjundomaranhao@hotmail.com</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-15.</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>João Lisboa</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — CONTRATAÇÃO DE EMPRESA PARA FORNECIMENTO DE ITENS PARA ENXOVAL PARA DISTRIBUIÇÃO PARA GESTANTES DO MUNICÍPIO DE JOÃO LISBOA - MA</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE JOAO LISBOA</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>licitacaojoaolisboa@gmail.com</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-09.</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Lago do Junco</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISPENSA — O objeto do presente instrumento é a Contratação de empresa especializada para o fornecimento de itens de Enxoval Maternidade, destinado a atender as </t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE LAGO DO JUNCO</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>cplldj2025@gmail.com</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-02.</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Arceburgo</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISPENSA — CONTRATAÇÃO DE EMPRESA PARA O FORNECIMENTO DE ITENS DESTINADOS À COMPOSIÇÃO DE KITS DE ENXOVAL PARA BEBÊ, A SEREM DISTRIBUÍDOS ÀS GESTANTES ATENDIDAS </t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE ARCEBURGO</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>licitacao.arceburgo@gmail.com</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-16.</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — O objeto da presente dispensa eletrônica é a escolha da proposta mais vantajosa para a itens de enxoval destinados auxiliar o processo de manutenção d</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>CONSORCIO REGIONAL DE PROMOCAO DA CIDADANIA - MULHERES DAS G</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>(31) 3484-2387</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. ATENÇÃO: um telefone foi descartado por ser da plataforma de licitação, não do município. Publicado 2026-08-26.</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Uiraúna</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — Contratação de empresa para o fornecimento parcelado de kits de enxoval básico destinados a recém-nascidos, visando atender às necessidades do Program</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE UIRAUNA</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>cpl@uirauna.pb.gov.br</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-08-11.</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Picuí</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — AQUISIÇÃO DE KITs DE ENXOVAL DE BEBÊ DE FORMA PARCELADA, DESTINADA À CONCESSÃO DE BENEFÍCIOS EVENTUAIS, no valor de 44.100,00 (Quarenta e quatro mil e</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PICUI</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>(83) 3371-2380</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-08-10.</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Saloá</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISPENSA — AQUISICAO DE KITS DE ENXOVAIS DE RECEM-NASCIDOS PARA DOACAO AS FAMILIAS CARENTES DO MUNICIPIO DE SALOA/PE, NO AMBITO DE PROGRAMA SOCIOASSISTENCIAL DO </t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SALOA</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>saloalicitacao@gmail.com</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>(87) 3782-1181 · (87) 99651-0139</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-10.</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Petrolina</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — [Portal de Compras Públicas] - A contratação de empresa especializada para o fornecimento de Kit Natalidade.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE PETROLINA</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>licitacoes@petrolina.pe.gov.br</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>(87) 3983-6419</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-08.</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>São Bento do Una</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — [Portal de Compras Públicas] - Contratação de empresa para aquisição de Kits natalidades - enxovais para eventual fornecimento a recém-nascido (neonat</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE ASSISTENCIA SOCIAL DE SAO BENTO DO UNA</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>acaosocial@saobentodouna.pe.gov.br</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>(81) 3735-1488</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-08-13.</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Nazaré do Piauí</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — Aquisição de kit natalidade para secretaria de assistência social</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE NAZARE DO PIAUI</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>licitanazaredopiaui@gmail.com</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-21.</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Marcos Parente</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISPENSA — Aquisição de kit natalidade para a Secretaria de Assistência Social de Marcos Parente -PI. </t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE MARCOS PARENTE</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>cplmarcosparente2021@gmail.com</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>(89) 3541-1277</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-21.</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Rio Branco do Sul</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — A contratação visa o fornecimento de kit natalidade, com entrega parcelada, conforme a necessidade da Secretaria, durante o período de 12 meses</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE RIO BRANCO DO SUL</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>protecaosocial@riobrancodosul.pr.gov.br · francelise.souza@riobrancodosul.pr.gov.br · smasrbs2019@gmail.com</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>(41) 98743-2024 · (41) 99650-9949 · (41) 98879-6219</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-15.</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Serra Caiada</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — Aquisição de itens para enxoval do GRUPO DE GESTANTE DO PAIF referenciado pelo Centro de Referência da Assistência Social do Município de Serra Caiada</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE SERRA CAIADA</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>setordelicitacao@serracaiada.rn.gov.br</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>(84) 3293-0038</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-09-08.</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Torrinha</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>DISPENSA — Aquisição de kit de higiene para bebe, com a finalidade de entrega para as gestantes da rede municipal de saúde.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE TORRINHA</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>licitacao@torrinha.sp.gov.br</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>(14) 3656-9600</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. Publicado 2026-08-10.</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Juquitiba</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DISPENSA — A aquisição de Kit enxoval maternidade destinado a Secretaria Municipal de Assistência Social (CRAS). Visando reduzir as vulnerabilidades decorrentes </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>MUNICIPIO DE JUQUITIBA</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>compras.2@juquitiba.sp.gov.br · administracao@juquitiba.sp.gov.br</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>(11) 4681-4311</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Lido automaticamente do edital publicado. ATENÇÃO: um telefone foi descartado por ser da plataforma de licitação, não do município. Publicado 2026-08-07.</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Contatos completos e linha a linha em data/municipios_contatos.csv (60 registros) e data/municipios_contatos.md. Nada aqui foi inventado: cada valor foi lido numa página oficial do município, no diário oficial ou no edital publicado. Onde não deu para ler, está escrito que não deu.</t>
         </is>
@@ -1440,7 +2152,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
